--- a/study_case_model/scenario_variables/other_experiment_data/demand_scenarios186.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/demand_scenarios186.xlsx
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17804.83779513908</v>
+        <v>27521.7481480029</v>
       </c>
     </row>
     <row r="3">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16135.03358576632</v>
+        <v>25748.21626575549</v>
       </c>
     </row>
     <row r="6">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>10482.71012625072</v>
+        <v>3127.739226430319</v>
       </c>
     </row>
     <row r="9">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18902.59059545644</v>
+        <v>14728.3641594399</v>
       </c>
     </row>
     <row r="12">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4725.64764886411</v>
+        <v>3682.091039859976</v>
       </c>
     </row>
     <row r="14">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>32518.37710668415</v>
+        <v>50307.81004362414</v>
       </c>
     </row>
     <row r="15">
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>18014.98246494608</v>
+        <v>13244.99844763992</v>
       </c>
     </row>
     <row r="18">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>15060.38971035669</v>
+        <v>15888.74714546962</v>
       </c>
     </row>
     <row r="21">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>35095.7756789686</v>
+        <v>19534.21353492791</v>
       </c>
     </row>
     <row r="24">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>16944.36136789753</v>
+        <v>14575.42631469057</v>
       </c>
     </row>
     <row r="27">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>25389.81529813421</v>
+        <v>11700.73562159986</v>
       </c>
     </row>
     <row r="30">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6347.453824533553</v>
+        <v>2925.183905399964</v>
       </c>
     </row>
     <row r="32">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>39593.50088754874</v>
+        <v>52005.94585585309</v>
       </c>
     </row>
     <row r="33">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>13784.19079691338</v>
+        <v>17142.32574308396</v>
       </c>
     </row>
     <row r="36">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>15419.71649837037</v>
+        <v>27891.02221833866</v>
       </c>
     </row>
     <row r="39">
@@ -1280,7 +1280,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>31831.80276275312</v>
+        <v>27516.15057374483</v>
       </c>
     </row>
     <row r="42">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>12222.55706923899</v>
+        <v>4924.432065583387</v>
       </c>
     </row>
     <row r="45">
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>17544.07871247989</v>
+        <v>15068.52334149263</v>
       </c>
     </row>
     <row r="48">
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4386.019678119973</v>
+        <v>3767.130835373157</v>
       </c>
     </row>
     <row r="50">
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>31643.82730015596</v>
+        <v>80813.02750386561</v>
       </c>
     </row>
     <row r="51">
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3209.352055141188</v>
+        <v>10253.14280920275</v>
       </c>
     </row>
     <row r="54">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>17210.94357223183</v>
+        <v>34483.57157160301</v>
       </c>
     </row>
     <row r="57">
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>33345.9864670968</v>
+        <v>20418.69332982788</v>
       </c>
     </row>
     <row r="60">
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>10989.37464321949</v>
+        <v>11458.17311933951</v>
       </c>
     </row>
     <row r="63">
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>18984.02685730972</v>
+        <v>23093.52107212112</v>
       </c>
     </row>
     <row r="66">
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4746.006714327429</v>
+        <v>5773.380268030279</v>
       </c>
     </row>
     <row r="68">
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>59833.31537432679</v>
+        <v>51510.39523991015</v>
       </c>
     </row>
     <row r="69">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>19271.258292936</v>
+        <v>13930.67169125405</v>
       </c>
     </row>
     <row r="72">
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>34937.53491209229</v>
+        <v>18862.0730895476</v>
       </c>
     </row>
     <row r="75">
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>17707.48747137859</v>
+        <v>16477.97357898433</v>
       </c>
     </row>
     <row r="78">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5215.360357109726</v>
+        <v>9177.981446035621</v>
       </c>
     </row>
     <row r="81">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>34157.68555460062</v>
+        <v>16806.0911512258</v>
       </c>
     </row>
     <row r="84">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>8539.421388650155</v>
+        <v>4201.52278780645</v>
       </c>
     </row>
     <row r="86">
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>84034.8741748918</v>
+        <v>46560.77926913883</v>
       </c>
     </row>
     <row r="87">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>13206.70098660981</v>
+        <v>16389.78267739933</v>
       </c>
     </row>
     <row r="90">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>15471.33815813634</v>
+        <v>25655.06092018786</v>
       </c>
     </row>
     <row r="93">
@@ -2414,7 +2414,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>32224.19900420455</v>
+        <v>28634.47826881439</v>
       </c>
     </row>
     <row r="96">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>12095.06117745271</v>
+        <v>13031.00379717549</v>
       </c>
     </row>
     <row r="99">
@@ -2540,7 +2540,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>19322.11326136034</v>
+        <v>13307.39447882734</v>
       </c>
     </row>
     <row r="102">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4830.528315340084</v>
+        <v>3326.848619706836</v>
       </c>
     </row>
     <row r="104">
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>63416.88264657693</v>
+        <v>50259.04289008474</v>
       </c>
     </row>
     <row r="105">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>13753.90530077487</v>
+        <v>12990.43291321826</v>
       </c>
     </row>
     <row r="108">
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>16106.38816738791</v>
+        <v>30699.42416005981</v>
       </c>
     </row>
     <row r="111">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>22564.4354868852</v>
+        <v>16985.58947767401</v>
       </c>
     </row>
     <row r="114">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>14979.32348248005</v>
+        <v>4848.459255693648</v>
       </c>
     </row>
     <row r="117">
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>23061.51333443011</v>
+        <v>21057.58289102299</v>
       </c>
     </row>
     <row r="120">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5765.378333607528</v>
+        <v>5264.395722755747</v>
       </c>
     </row>
     <row r="122">
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>53930.24861537714</v>
+        <v>55307.75002382571</v>
       </c>
     </row>
     <row r="123">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>16000.33607928449</v>
+        <v>11827.30697631107</v>
       </c>
     </row>
     <row r="126">
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>22287.12259137051</v>
+        <v>25210.15675545093</v>
       </c>
     </row>
     <row r="129">
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>26340.02331414304</v>
+        <v>31590.79283937104</v>
       </c>
     </row>
     <row r="132">
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0</v>
+        <v>10779.47908802184</v>
       </c>
     </row>
     <row r="135">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>17302.09883694312</v>
+        <v>18328.15494704853</v>
       </c>
     </row>
     <row r="138">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4325.524709235779</v>
+        <v>4582.038736762132</v>
       </c>
     </row>
     <row r="140">
@@ -3359,7 +3359,7 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>61458.54362863467</v>
+        <v>51185.54666920748</v>
       </c>
     </row>
     <row r="141">
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>11036.02074831072</v>
+        <v>7925.694953114965</v>
       </c>
     </row>
     <row r="144">
